--- a/backend/sample_master_theses.xlsx
+++ b/backend/sample_master_theses.xlsx
@@ -397,109 +397,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Group Name</v>
+        <v>Project Title</v>
       </c>
       <c r="B1" t="str">
-        <v>Project Title</v>
+        <v>Member Names</v>
       </c>
       <c r="C1" t="str">
-        <v>Member Names</v>
-      </c>
-      <c r="D1" t="str">
         <v>Roll Numbers</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>Deep Learning for Nepali Sign Language Recognition</v>
       </c>
       <c r="B2" t="str">
-        <v>Deep Learning for Nepali Handwriting Recognition</v>
+        <v>Pooja Magar</v>
       </c>
       <c r="C2" t="str">
-        <v>Bibek Chaudhary</v>
-      </c>
-      <c r="D2" t="str">
-        <v>CSE021</v>
+        <v>080BCT001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>Federated Learning for Privacy-Preserving Medical Diagnosis</v>
       </c>
       <c r="B3" t="str">
-        <v>Optimizing Transformer Models for Low-Resource Languages</v>
+        <v>Rajan Puri</v>
       </c>
       <c r="C3" t="str">
-        <v>Muna Gautam</v>
-      </c>
-      <c r="D3" t="str">
-        <v>CSE022</v>
+        <v>080BCT008</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>NLP-based Automatic Question Paper Generator in Nepali</v>
       </c>
       <c r="B4" t="str">
-        <v>Federated Learning in Healthcare: A Privacy-Preserving Approach</v>
+        <v>Sushma Karki</v>
       </c>
       <c r="C4" t="str">
-        <v>Rajan Puri</v>
-      </c>
-      <c r="D4" t="str">
-        <v>CSE023</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v>Explainable AI for Credit Risk Assessment</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Sushma Karki</v>
-      </c>
-      <c r="D5" t="str">
-        <v>CSE024</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v>Autonomous Navigation using Reinforcement Learning</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Dipesh Giri</v>
-      </c>
-      <c r="D6" t="str">
-        <v>CSE025</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v>GAN-based Data Augmentation for Medical Imaging</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Kabita Bista</v>
-      </c>
-      <c r="D7" t="str">
-        <v>CSE026</v>
+        <v>080BCT009</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>